--- a/01-dcf-valuation/Tesla_DCF_Model.xlsx
+++ b/01-dcf-valuation/Tesla_DCF_Model.xlsx
@@ -19,7 +19,7 @@
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Assumptions!$A$1:$G$34</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Checks!$A$1:$E$17</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Cover!$A$1:$C$16</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">DCF!$A$1:$S$30</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">DCF!$A$1:$G$41</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'Market Gap'!$A$1:$S$20</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Sensitivity!$A$1:$G$16</definedName>
   </definedNames>
@@ -32,8 +32,76 @@
 </workbook>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="C21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Identique au bêta de régression de marché (C13, stockanalysis.com). La cellule est laissée éditable séparément de C13 pour permettre de tester un bêta ajusté (par exemple un bêta reconstruit par rebêtisation d'un panier de comparables) sans modifier la donnée de marché brute, mais aucun ajustement de ce type n'a été appliqué ici : les deux valeurs sont identiques dans ce modèle.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Convention mid-year : les flux de trésorerie sont supposés perçus en moyenne au milieu de chaque exercice (période n-0,5), plutôt qu'en toute fin d'année. Convention standard en modélisation DCF (guide BIWS, Breaking Into Wall Street) ; la valeur terminale (Gordon growth) est actualisée avec le même facteur que le dernier flux explicite, sans 0,5 supplémentaire, conformément à cette méthode.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Hypothèse : la marge est maintenue constante jusqu'en 2030 pour ce recoupement.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Référence interne (DCF!C24), car aucun comparable boursier EV/EBITDA n'est sourcé pour Tesla dans ce classeur.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="109">
   <si>
     <t xml:space="preserve">Tesla, Inc. (NASDAQ : TSLA) - DCF à 2 étages sur une valeur de croissance</t>
   </si>
@@ -206,7 +274,7 @@
     <t xml:space="preserve">2028-2030 : hypothèse personnelle de ralentissement progressif vers un taux proche de la croissance terminale.</t>
   </si>
   <si>
-    <t xml:space="preserve">Marge de FCF : hypothèse personnelle d'amélioration progressive à mesure que l'intensité du capex (Gigafactories, IA/Optimus) se normalise - FY2025 réel = 6,6 % (6 220 / 94 827).</t>
+    <t xml:space="preserve">Marge de FCF : hypothèse personnelle d'amélioration progressive à mesure que l'intensité du capex (Gigafactories, IA/Optimus) se normalise. FY2025 réel = 6,6 % (6 220 / 94 827).</t>
   </si>
   <si>
     <t xml:space="preserve">DCF à 2 étages</t>
@@ -221,7 +289,7 @@
     <t xml:space="preserve">Free cash-flow ($M)</t>
   </si>
   <si>
-    <t xml:space="preserve">Facteur d'actualisation</t>
+    <t xml:space="preserve">Facteur d'actualisation (convention mid-year)</t>
   </si>
   <si>
     <t xml:space="preserve">VA du FCF ($M)</t>
@@ -263,7 +331,25 @@
     <t xml:space="preserve">VE/EBITDA impliqué par le marché ((capi - trésorerie nette) / EBITDA FY2025)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture : ce DCF, construit uniquement sur les flux de l'activité automobile/énergie actuelle, fait ressortir une valeur par action très inférieure au cours de marché. L'écart ne traduit pas une erreur de calcul mais le fait que la capitalisation de Tesla intègre des paris sur des relais de croissance non reflétés dans les flux actuels (robotaxi/FSD, Optimus, stockage d'énergie) - voir l'onglet Market Gap.</t>
+    <t xml:space="preserve">Lecture : ce DCF, construit uniquement sur les flux de l'activité automobile/énergie actuelle, fait ressortir une valeur par action très inférieure au cours de marché. L'écart ne traduit pas une erreur de calcul mais le fait que la capitalisation de Tesla intègre des paris sur des relais de croissance non reflétés dans les flux actuels (robotaxi/FSD, Optimus, stockage d'énergie) ; voir l'onglet Market Gap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECOUPEMENT DE LA VALEUR TERMINALE (MULTIPLE DE SORTIE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marge d'EBITDA ajusté FY2025 (hypothèse de projection)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBITDA implicite, année 5 (2030, $M)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple de sortie implicite (VT / EBITDA an 5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour mémoire : multiple implicite du DCF sur EBITDA actuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecture : ce recoupement applique la méthode des multiples de sortie en complément de la méthode Gordon growth (cf. guide BIWS, Key Rule #4). Aucun comparable boursier (EV/EBITDA) n'étant sourcé dans ce modèle pour un acteur automobile ou technologique comparable à Tesla sur son profil actuel, le multiple de sortie implicite est présenté à titre de contrôle de cohérence interne (il reste dans un ordre de grandeur proche du multiple déjà implicite du DCF sur l'EBITDA actuel), et non comme un recoupement contre des comparables externes.</t>
   </si>
   <si>
     <t xml:space="preserve">Sensibilité - valeur implicite par action ($)</t>
@@ -272,7 +358,7 @@
     <t xml:space="preserve">WACC \ g terminale</t>
   </si>
   <si>
-    <t xml:space="preserve">Formule : somme des FCF actualisés sur la trajectoire de l'onglet DCF + valeur terminale (Gordon growth) au couple (WACC, g), plus trésorerie nette, divisé par le nombre d'actions.</t>
+    <t xml:space="preserve">Formule : somme des FCF actualisés (convention mid-year) sur la trajectoire de l'onglet DCF + valeur terminale (Gordon growth) au couple (WACC, g), plus trésorerie nette, divisé par le nombre d'actions.</t>
   </si>
   <si>
     <t xml:space="preserve">Lecture de l'écart DCF / marché</t>
@@ -302,7 +388,7 @@
     <t xml:space="preserve">- Stockage d'énergie (Megapack) : segment en forte croissance mais encore minoritaire dans le chiffre d'affaires total.</t>
   </si>
   <si>
-    <t xml:space="preserve">- Prime d'exécution/attentes : le marché valorise Tesla avec un multiple proche de 100x l'EBITDA actuel (voir DCF!C25), contre 8,6x pour la valeur implicite du DCF (DCF!C24) - un écart qui ne se retrouve sur aucun constructeur automobile traditionnel.</t>
+    <t xml:space="preserve">- Prime d'exécution/attentes : le marché valorise Tesla avec un multiple proche de 100x l'EBITDA actuel (voir DCF!C25), contre environ 9x pour la valeur implicite du DCF (DCF!C24), un écart qui ne se retrouve sur aucun constructeur automobile traditionnel.</t>
   </si>
   <si>
     <t xml:space="preserve">Conclusion de l'exercice</t>
@@ -333,6 +419,9 @@
   </si>
   <si>
     <t xml:space="preserve">Actions × cours cohérent avec la capitalisation (écart &lt; 6 %, cf. note sur les bases de calcul)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple de sortie implicite calculable et positif (contrôle interne ; pas de comparable externe sourcé ici)</t>
   </si>
   <si>
     <t xml:space="preserve">Synthèse</t>
@@ -359,7 +448,7 @@
     <numFmt numFmtId="174" formatCode="#,##0.0&quot; $&quot;"/>
     <numFmt numFmtId="175" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -425,6 +514,11 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -606,11 +700,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -618,7 +712,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -638,23 +732,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="174" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -662,7 +756,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -918,11 +1012,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="48913771"/>
-        <c:axId val="18329172"/>
+        <c:axId val="41912831"/>
+        <c:axId val="94447015"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="48913771"/>
+        <c:axId val="41912831"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -953,7 +1047,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18329172"/>
+        <c:crossAx val="94447015"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -961,7 +1055,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="18329172"/>
+        <c:axId val="94447015"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1036,7 +1130,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48913771"/>
+        <c:crossAx val="41912831"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1174,7 +1268,7 @@
                 <c:formatCode>#,##0.0" $"</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>43.0890633733913</c:v>
+                  <c:v>45.2839586228583</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>379.26</c:v>
@@ -1185,11 +1279,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="56045222"/>
-        <c:axId val="78864082"/>
+        <c:axId val="31122338"/>
+        <c:axId val="97733729"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="56045222"/>
+        <c:axId val="31122338"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1220,7 +1314,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78864082"/>
+        <c:crossAx val="97733729"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1228,7 +1322,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78864082"/>
+        <c:axId val="97733729"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1303,7 +1397,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56045222"/>
+        <c:crossAx val="31122338"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1342,9 +1436,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>253440</xdr:colOff>
+      <xdr:colOff>249480</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>19800</xdr:rowOff>
+      <xdr:rowOff>15840</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1353,7 +1447,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9328680" y="600120"/>
-        <a:ext cx="5757120" cy="2877120"/>
+        <a:ext cx="5753160" cy="2873160"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1377,9 +1471,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>253800</xdr:colOff>
+      <xdr:colOff>249840</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>19440</xdr:rowOff>
+      <xdr:rowOff>15480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1388,7 +1482,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="10976760" y="1171440"/>
-        <a:ext cx="5757120" cy="2877120"/>
+        <a:ext cx="5753160" cy="2873160"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1958,6 +2052,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1966,7 +2061,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G30"/>
+  <dimension ref="B2:G41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="50"/>
@@ -2078,24 +2173,24 @@
         <v>62</v>
       </c>
       <c r="C9" s="14" t="n">
-        <f aca="false">1/(1+Assumptions!$C$23)^1</f>
-        <v>0.881057268722467</v>
+        <f aca="false">1/(1+Assumptions!$C$23)^0.5</f>
+        <v>0.938646508927864</v>
       </c>
       <c r="D9" s="14" t="n">
-        <f aca="false">1/(1+Assumptions!$C$23)^2</f>
-        <v>0.776261910768693</v>
+        <f aca="false">1/(1+Assumptions!$C$23)^1.5</f>
+        <v>0.827001329451863</v>
       </c>
       <c r="E9" s="14" t="n">
-        <f aca="false">1/(1+Assumptions!$C$23)^3</f>
-        <v>0.683931198915148</v>
+        <f aca="false">1/(1+Assumptions!$C$23)^2.5</f>
+        <v>0.728635532556707</v>
       </c>
       <c r="F9" s="14" t="n">
-        <f aca="false">1/(1+Assumptions!$C$23)^4</f>
-        <v>0.602582554110263</v>
+        <f aca="false">1/(1+Assumptions!$C$23)^3.5</f>
+        <v>0.641969632208553</v>
       </c>
       <c r="G9" s="14" t="n">
-        <f aca="false">1/(1+Assumptions!$C$23)^5</f>
-        <v>0.530909739304196</v>
+        <f aca="false">1/(1+Assumptions!$C$23)^4.5</f>
+        <v>0.565612010756434</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2104,23 +2199,23 @@
       </c>
       <c r="C10" s="11" t="n">
         <f aca="false">C7*C9</f>
-        <v>6602.79983259912</v>
+        <v>7034.38383864117</v>
       </c>
       <c r="D10" s="11" t="n">
         <f aca="false">D7*D9</f>
-        <v>7559.35396819655</v>
+        <v>8053.46197561738</v>
       </c>
       <c r="E10" s="11" t="n">
         <f aca="false">E7*E9</f>
-        <v>8242.02690365042</v>
+        <v>8780.75699984714</v>
       </c>
       <c r="F10" s="11" t="n">
         <f aca="false">F7*F9</f>
-        <v>8633.35172482228</v>
+        <v>9197.66029352564</v>
       </c>
       <c r="G10" s="11" t="n">
         <f aca="false">G7*G9</f>
-        <v>8785.48127063412</v>
+        <v>9359.73360266266</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2129,7 +2224,7 @@
       </c>
       <c r="C12" s="11" t="n">
         <f aca="false">SUM(C10:G10)</f>
-        <v>39823.0136999025</v>
+        <v>42425.996710294</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2147,7 +2242,7 @@
       </c>
       <c r="C15" s="11" t="n">
         <f aca="false">C14*G9</f>
-        <v>86181.3877024109</v>
+        <v>91814.5296261194</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2156,7 +2251,7 @@
       </c>
       <c r="C17" s="15" t="n">
         <f aca="false">C12+C15</f>
-        <v>126004.401402313</v>
+        <v>134240.526336413</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2174,7 +2269,7 @@
       </c>
       <c r="C19" s="15" t="n">
         <f aca="false">C17+C18</f>
-        <v>161687.401402313</v>
+        <v>169923.526336413</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2192,7 +2287,7 @@
       </c>
       <c r="C21" s="18" t="n">
         <f aca="false">C19/C20</f>
-        <v>43.0890633733913</v>
+        <v>45.2839586228583</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2210,7 +2305,7 @@
       </c>
       <c r="C23" s="13" t="n">
         <f aca="false">C21/C22-1</f>
-        <v>-0.886386480584846</v>
+        <v>-0.880599170429631</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2219,7 +2314,7 @@
       </c>
       <c r="C24" s="20" t="n">
         <f aca="false">C17/Assumptions!C6</f>
-        <v>8.63280360388554</v>
+        <v>9.1970763453284</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2265,9 +2360,90 @@
       <c r="F30" s="21"/>
       <c r="G30" s="21"/>
     </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="13" t="n">
+        <f aca="false">Assumptions!C6/Assumptions!C5</f>
+        <v>0.153922406065783</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <f aca="false">G5*C33</f>
+        <v>23155.4925358218</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="20" t="n">
+        <f aca="false">C14/C34</f>
+        <v>7.01033492541988</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="20" t="n">
+        <f aca="false">C24</f>
+        <v>9.1970763453284</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+    </row>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B27:G30"/>
+    <mergeCell ref="B38:G41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2276,7 +2452,11 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="30" man="true" max="16383" min="0"/>
+  </rowBreaks>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -2294,12 +2474,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C4" s="22" t="n">
         <v>0.02</v>
@@ -2319,20 +2499,20 @@
         <v>0.11</v>
       </c>
       <c r="C5" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B5)^{1,2,3,4,5})+DCF!$G$7*(1+C$4)/($B5-C$4)/(1+$B5)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>50.5559271743194</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B5)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+C$4)/($B5-C$4)/(1+$B5)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>52.7546008423604</v>
       </c>
       <c r="D5" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B5)^{1,2,3,4,5})+DCF!$G$7*(1+D$4)/($B5-D$4)/(1+$B5)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>52.454609866974</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B5)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+D$4)/($B5-D$4)/(1+$B5)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>54.7549871859946</v>
       </c>
       <c r="E5" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B5)^{1,2,3,4,5})+DCF!$G$7*(1+E$4)/($B5-E$4)/(1+$B5)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>54.5906278962103</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B5)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+E$4)/($B5-E$4)/(1+$B5)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>57.0054218225831</v>
       </c>
       <c r="F5" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B5)^{1,2,3,4,5})+DCF!$G$7*(1+F$4)/($B5-F$4)/(1+$B5)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>57.0114483293448</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B5)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+F$4)/($B5-F$4)/(1+$B5)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>59.5559144107167</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2340,20 +2520,20 @@
         <v>0.12</v>
       </c>
       <c r="C6" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B6)^{1,2,3,4,5})+DCF!$G$7*(1+C$4)/($B6-C$4)/(1+$B6)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>46.1000052056199</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B6)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+C$4)/($B6-C$4)/(1+$B6)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>48.2332578055211</v>
       </c>
       <c r="D6" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B6)^{1,2,3,4,5})+DCF!$G$7*(1+D$4)/($B6-D$4)/(1+$B6)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>47.5750664276044</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B6)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+D$4)/($B6-D$4)/(1+$B6)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>49.7943158703075</v>
       </c>
       <c r="E6" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B6)^{1,2,3,4,5})+DCF!$G$7*(1+E$4)/($B6-E$4)/(1+$B6)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>49.2140233409205</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B6)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+E$4)/($B6-E$4)/(1+$B6)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>51.5288248311812</v>
       </c>
       <c r="F6" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B6)^{1,2,3,4,5})+DCF!$G$7*(1+F$4)/($B6-F$4)/(1+$B6)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>51.0457987146267</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B6)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+F$4)/($B6-F$4)/(1+$B6)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>53.4673936698048</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2361,20 +2541,20 @@
         <v>0.125</v>
       </c>
       <c r="C7" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B7)^{1,2,3,4,5})+DCF!$G$7*(1+C$4)/($B7-C$4)/(1+$B7)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>44.1945940910033</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B7)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+C$4)/($B7-C$4)/(1+$B7)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>46.2986050957631</v>
       </c>
       <c r="D7" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B7)^{1,2,3,4,5})+DCF!$G$7*(1+D$4)/($B7-D$4)/(1+$B7)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>45.5056051435986</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B7)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+D$4)/($B7-D$4)/(1+$B7)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>47.6891423040141</v>
       </c>
       <c r="E7" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B7)^{1,2,3,4,5})+DCF!$G$7*(1+E$4)/($B7-E$4)/(1+$B7)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>46.954617359625</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B7)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+E$4)/($B7-E$4)/(1+$B7)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>49.2260518499757</v>
       </c>
       <c r="F7" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B7)^{1,2,3,4,5})+DCF!$G$7*(1+F$4)/($B7-F$4)/(1+$B7)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>48.5646309329876</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B7)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+F$4)/($B7-F$4)/(1+$B7)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>50.9337291232664</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2382,20 +2562,20 @@
         <v>0.135</v>
       </c>
       <c r="C8" s="24" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B8)^{1,2,3,4,5})+DCF!$G$7*(1+C$4)/($B8-C$4)/(1+$B8)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>40.8883415403373</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B8)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+C$4)/($B8-C$4)/(1+$B8)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>42.939389275269</v>
       </c>
       <c r="D8" s="24" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B8)^{1,2,3,4,5})+DCF!$G$7*(1+D$4)/($B8-D$4)/(1+$B8)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>41.9386860515676</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B8)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+D$4)/($B8-D$4)/(1+$B8)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>44.0583882820729</v>
       </c>
       <c r="E8" s="24" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B8)^{1,2,3,4,5})+DCF!$G$7*(1+E$4)/($B8-E$4)/(1+$B8)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>43.0890633733913</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B8)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+E$4)/($B8-E$4)/(1+$B8)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>45.2839586228583</v>
       </c>
       <c r="F8" s="24" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B8)^{1,2,3,4,5})+DCF!$G$7*(1+F$4)/($B8-F$4)/(1+$B8)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>44.3544784273973</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B8)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+F$4)/($B8-F$4)/(1+$B8)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>46.6320859977221</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2403,20 +2583,20 @@
         <v>0.14</v>
       </c>
       <c r="C9" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B9)^{1,2,3,4,5})+DCF!$G$7*(1+C$4)/($B9-C$4)/(1+$B9)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>39.4453456705707</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B9)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+C$4)/($B9-C$4)/(1+$B9)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>41.4722447565875</v>
       </c>
       <c r="D9" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B9)^{1,2,3,4,5})+DCF!$G$7*(1+D$4)/($B9-D$4)/(1+$B9)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>40.3913807709782</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B9)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+D$4)/($B9-D$4)/(1+$B9)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>42.4823338362095</v>
       </c>
       <c r="E9" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B9)^{1,2,3,4,5})+DCF!$G$7*(1+E$4)/($B9-E$4)/(1+$B9)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>41.4234190623319</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B9)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+E$4)/($B9-E$4)/(1+$B9)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>43.5842491957971</v>
       </c>
       <c r="F9" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B9)^{1,2,3,4,5})+DCF!$G$7*(1+F$4)/($B9-F$4)/(1+$B9)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>42.5537467147669</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B9)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+F$4)/($B9-F$4)/(1+$B9)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>44.7911088753454</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2424,20 +2604,20 @@
         <v>0.15</v>
       </c>
       <c r="C10" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B10)^{1,2,3,4,5})+DCF!$G$7*(1+C$4)/($B10-C$4)/(1+$B10)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>36.8985585627571</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B10)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+C$4)/($B10-C$4)/(1+$B10)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>38.8810017610607</v>
       </c>
       <c r="D10" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B10)^{1,2,3,4,5})+DCF!$G$7*(1+D$4)/($B10-D$4)/(1+$B10)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>37.6743786414153</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B10)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+D$4)/($B10-D$4)/(1+$B10)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>39.7129761077905</v>
       </c>
       <c r="E10" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B10)^{1,2,3,4,5})+DCF!$G$7*(1+E$4)/($B10-E$4)/(1+$B10)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>38.5148503932949</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B10)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+E$4)/($B10-E$4)/(1+$B10)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>40.6142816500811</v>
       </c>
       <c r="F10" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B10)^{1,2,3,4,5})+DCF!$G$7*(1+F$4)/($B10-F$4)/(1+$B10)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>39.428406645338</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B10)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+F$4)/($B10-F$4)/(1+$B10)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>41.5939615873536</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2445,25 +2625,25 @@
         <v>0.16</v>
       </c>
       <c r="C11" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B11)^{1,2,3,4,5})+DCF!$G$7*(1+C$4)/($B11-C$4)/(1+$B11)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>34.7230018854895</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B11)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+C$4)/($B11-C$4)/(1+$B11)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>36.6652817965507</v>
       </c>
       <c r="D11" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B11)^{1,2,3,4,5})+DCF!$G$7*(1+D$4)/($B11-D$4)/(1+$B11)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>35.3673372685137</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B11)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+D$4)/($B11-D$4)/(1+$B11)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>37.3592522422815</v>
       </c>
       <c r="E11" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B11)^{1,2,3,4,5})+DCF!$G$7*(1+E$4)/($B11-E$4)/(1+$B11)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>36.0612369117707</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B11)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+E$4)/($B11-E$4)/(1+$B11)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>38.1066050299916</v>
       </c>
       <c r="F11" s="23" t="n">
-        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B11)^{1,2,3,4,5})+DCF!$G$7*(1+F$4)/($B11-F$4)/(1+$B11)^5+Assumptions!$C$15)/Assumptions!$C$10</f>
-        <v>36.8106485264881</v>
+        <f aca="false">(SUMPRODUCT(DCF!$C$7:$G$7,1/(1+$B11)^{0.5,1.5,2.5,3.5,4.5})+DCF!$G$7*(1+F$4)/($B11-F$4)/(1+$B11)^4.5+Assumptions!$C$15)/Assumptions!$C$10</f>
+        <v>38.9137460407184</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="21" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C14" s="21"/>
       <c r="D14" s="21"/>
@@ -2514,31 +2694,31 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="J4" s="26" t="n">
         <f aca="false">DCF!C21</f>
-        <v>43.0890633733913</v>
+        <v>45.2839586228583</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="21" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C5" s="21"/>
       <c r="D5" s="21"/>
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
       <c r="I5" s="25" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="J5" s="26" t="n">
         <f aca="false">DCF!C22</f>
@@ -2554,12 +2734,12 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="27" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C9" s="27"/>
       <c r="D9" s="27"/>
@@ -2568,7 +2748,7 @@
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="27" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C10" s="27"/>
       <c r="D10" s="27"/>
@@ -2577,7 +2757,7 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="27" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C11" s="27"/>
       <c r="D11" s="27"/>
@@ -2586,7 +2766,7 @@
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="27" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
@@ -2595,12 +2775,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="21" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C16" s="21"/>
       <c r="D16" s="21"/>
@@ -2662,20 +2842,20 @@
   <sheetData>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="28" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="29" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D6" s="4" t="str">
         <f aca="false">IF(Assumptions!C24&lt;Assumptions!C23,"OK","A VERIFIER")</f>
@@ -2684,7 +2864,7 @@
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D7" s="4" t="str">
         <f aca="false">IF(MIN(Assumptions!C30:G30)&gt;0,"OK","A VERIFIER")</f>
@@ -2693,7 +2873,7 @@
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D8" s="4" t="str">
         <f aca="false">IF(ROUND(DCF!C12+DCF!C15-DCF!C17,1)=0,"OK","A VERIFIER")</f>
@@ -2702,7 +2882,7 @@
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D9" s="4" t="str">
         <f aca="false">IF(ROUND(DCF!C17+DCF!C18-DCF!C19,1)=0,"OK","A VERIFIER")</f>
@@ -2711,25 +2891,34 @@
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D10" s="4" t="str">
         <f aca="false">IF(ABS(Assumptions!C10*Assumptions!C11/Assumptions!C12-1)&lt;0.06,"OK","A VERIFIER")</f>
         <v>OK</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="4" t="str">
+        <f aca="false">IF(DCF!C35&gt;0,"OK","A VERIFIER")</f>
+        <v>OK</v>
+      </c>
+    </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C12" s="4" t="str">
-        <f aca="false">IF(COUNTIF(D6:D10,"OK")=5,"Tous les contrôles sont OK","Au moins un contrôle à vérifier")</f>
+        <f aca="false">IF(COUNTIF(D6:D11,"OK")=6,"Tous les contrôles sont OK","Au moins un contrôle à vérifier")</f>
         <v>Tous les contrôles sont OK</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="30" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C15" s="30"/>
       <c r="D15" s="30"/>
